--- a/data/trans_camb/P38B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 14,39</t>
+          <t>0,48; 13,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 10,02</t>
+          <t>-8,96; 10,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 10,35</t>
+          <t>-2,88; 9,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 7,45</t>
+          <t>-9,53; 7,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,26</t>
+          <t>1,54; 11,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 5,92</t>
+          <t>-7,67; 5,34</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 32,14</t>
+          <t>1,11; 31,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 21,32</t>
+          <t>-17,47; 22,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 17,95</t>
+          <t>-4,55; 17,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 12,86</t>
+          <t>-15,22; 13,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 19,8</t>
+          <t>2,64; 21,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 11,27</t>
+          <t>-13,68; 9,98</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -1,93</t>
+          <t>-12,51; -2,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -4,17</t>
+          <t>-17,17; -4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,98</t>
+          <t>-7,97; 0,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-43,91; -6,37</t>
+          <t>-45,49; -6,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -1,8</t>
+          <t>-8,38; -1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,87; -7,67</t>
+          <t>-31,34; -7,48</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -2,64</t>
+          <t>-15,95; -2,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,4; -5,35</t>
+          <t>-22,18; -5,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 1,18</t>
+          <t>-9,2; 1,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,42; -7,54</t>
+          <t>-53,18; -7,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -2,25</t>
+          <t>-10,21; -2,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,04; -9,56</t>
+          <t>-39,31; -9,33</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 0,49</t>
+          <t>-7,88; 0,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -3,66</t>
+          <t>-12,7; -3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -1,12</t>
+          <t>-8,49; -0,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,26; -2,45</t>
+          <t>-9,34; -2,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -1,68</t>
+          <t>-6,85; -1,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -4,17</t>
+          <t>-9,93; -4,13</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,6</t>
+          <t>-9,06; 0,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -4,33</t>
+          <t>-14,64; -4,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -1,28</t>
+          <t>-9,24; -1,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -2,78</t>
+          <t>-10,25; -2,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -1,95</t>
+          <t>-7,8; -1,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,13; -4,85</t>
+          <t>-11,21; -4,77</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,06</t>
+          <t>-6,45; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-61,4; -1,76</t>
+          <t>-63,32; -1,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,34</t>
+          <t>-3,42; 3,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,93</t>
+          <t>-1,37; 5,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,32</t>
+          <t>-3,79; 1,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 0,23</t>
+          <t>-40,84; 0,28</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,18</t>
+          <t>-7,02; 1,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,33; -1,96</t>
+          <t>-70,33; -1,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,75</t>
+          <t>-3,7; 4,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,58</t>
+          <t>-1,47; 5,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,48</t>
+          <t>-4,13; 1,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 0,26</t>
+          <t>-44,58; 0,32</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,49</t>
+          <t>-4,13; 2,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,47</t>
+          <t>-3,93; 2,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,41</t>
+          <t>-4,56; 1,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,25</t>
+          <t>-2,82; 2,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,39</t>
+          <t>-3,79; 1,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,68</t>
+          <t>-2,48; 1,88</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,72</t>
+          <t>-4,37; 2,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,69</t>
+          <t>-4,13; 3,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,48</t>
+          <t>-4,74; 1,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,41</t>
+          <t>-2,92; 2,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,49</t>
+          <t>-3,97; 1,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,8</t>
+          <t>-2,6; 2,03</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,55</t>
+          <t>-1,65; 4,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 2,09</t>
+          <t>-3,31; 2,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,17</t>
+          <t>0,11; 5,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,11</t>
+          <t>0,68; 6,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,15</t>
+          <t>-0,02; 3,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,99</t>
+          <t>-0,32; 3,76</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,85</t>
+          <t>-1,69; 4,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,2</t>
+          <t>-3,38; 2,71</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,52</t>
+          <t>0,12; 6,21</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,52</t>
+          <t>0,68; 6,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,42</t>
+          <t>0,03; 4,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,27</t>
+          <t>-0,33; 4,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,49; 9,35</t>
+          <t>1,37; 8,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,64</t>
+          <t>2,41; 10,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,36</t>
+          <t>-1,56; 3,36</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,49</t>
+          <t>-2,97; 1,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,64</t>
+          <t>0,39; 4,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,77</t>
+          <t>-0,14; 3,87</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,54; 10,46</t>
+          <t>1,46; 9,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,85</t>
+          <t>2,51; 11,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,5</t>
+          <t>-1,58; 3,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,57</t>
+          <t>-2,99; 1,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,98</t>
+          <t>0,42; 4,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,03</t>
+          <t>-0,14; 4,11</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,63</t>
+          <t>-2,1; 1,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -0,34</t>
+          <t>-25,67; -0,37</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,21</t>
+          <t>-1,85; 1,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,4</t>
+          <t>-6,68; 1,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,92</t>
+          <t>-1,63; 0,96</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -0,04</t>
+          <t>-14,53; -0,01</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,01</t>
+          <t>-2,53; 1,95</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,39; -0,44</t>
+          <t>-31,08; -0,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,38</t>
+          <t>-2,09; 1,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,61</t>
+          <t>-7,63; 1,58</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,1</t>
+          <t>-1,9; 1,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -0,05</t>
+          <t>-17,05; -0,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>-3,32</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-3,01</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 13,74</t>
+          <t>-0,28; 13,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 10,69</t>
+          <t>-12,72; 5,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 9,97</t>
+          <t>-2,96; 10,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 7,6</t>
+          <t>-11,03; 5,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,2</t>
+          <t>0,45; 10,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 5,34</t>
+          <t>-9,18; 3,7</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>-6,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,69%</t>
+          <t>-3,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,22%</t>
+          <t>-5,52%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 31,13</t>
+          <t>-0,48; 29,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 22,99</t>
+          <t>-24,69; 12,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 17,39</t>
+          <t>-4,55; 18,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 13,28</t>
+          <t>-17,56; 9,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 21,78</t>
+          <t>0,72; 19,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 9,98</t>
+          <t>-16,43; 7,21</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-10,54</t>
+          <t>-11,81</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-18,62</t>
+          <t>-9,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-14,29</t>
+          <t>-10,35</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,51; -2,13</t>
+          <t>-11,95; -2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -4,31</t>
+          <t>-18,77; -5,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 0,92</t>
+          <t>-7,87; 0,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-45,49; -6,34</t>
+          <t>-14,53; -4,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -1,91</t>
+          <t>-8,72; -1,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,34; -7,48</t>
+          <t>-14,21; -5,9</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-13,81%</t>
+          <t>-15,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-21,86%</t>
+          <t>-11,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,75%</t>
+          <t>-12,86%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,95; -2,82</t>
+          <t>-15,36; -3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -5,92</t>
+          <t>-24,15; -7,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 1,1</t>
+          <t>-9,05; 0,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -7,64</t>
+          <t>-16,86; -5,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -2,46</t>
+          <t>-10,55; -2,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,31; -9,33</t>
+          <t>-17,44; -7,34</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-8,15</t>
+          <t>-10,5</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,76</t>
+          <t>-6,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>-8,45</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 0,6</t>
+          <t>-7,98; 0,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,7; -3,35</t>
+          <t>-15,03; -5,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; -0,92</t>
+          <t>-8,42; -1,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,34; -2,32</t>
+          <t>-9,92; -2,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -1,51</t>
+          <t>-6,59; -1,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -4,13</t>
+          <t>-11,51; -5,55</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-9,55%</t>
+          <t>-12,31%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,39%</t>
+          <t>-6,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,96%</t>
+          <t>-9,63%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 0,69</t>
+          <t>-9,13; 0,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,64; -4,05</t>
+          <t>-17,45; -7,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,04</t>
+          <t>-9,27; -1,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -2,64</t>
+          <t>-10,79; -2,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -1,78</t>
+          <t>-7,39; -1,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -4,77</t>
+          <t>-12,93; -6,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-27,07</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-14,38</t>
+          <t>-1,11</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 1,04</t>
+          <t>-6,16; 1,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-63,32; -1,61</t>
+          <t>-6,0; 1,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,59</t>
+          <t>-3,21; 3,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 5,08</t>
+          <t>-2,31; 3,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,33</t>
+          <t>-3,7; 1,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 0,28</t>
+          <t>-3,35; 1,53</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-29,93%</t>
+          <t>-3,0%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,88%</t>
+          <t>-1,23%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 1,17</t>
+          <t>-6,77; 1,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,33; -1,84</t>
+          <t>-6,53; 1,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,07</t>
+          <t>-3,5; 3,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,73</t>
+          <t>-2,48; 4,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,49</t>
+          <t>-4,07; 1,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 0,32</t>
+          <t>-3,65; 1,74</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,73</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,7</t>
+          <t>-4,07; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,99</t>
+          <t>-4,69; 1,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,6</t>
+          <t>-4,88; 1,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 2,62</t>
+          <t>-2,18; 2,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,19</t>
+          <t>-3,49; 1,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,88</t>
+          <t>-2,75; 1,3</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0,53%</t>
+          <t>-1,44%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0,37%</t>
+          <t>-0,07%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,49%</t>
+          <t>-0,77%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,97</t>
+          <t>-4,32; 3,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 3,29</t>
+          <t>-4,94; 2,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,68</t>
+          <t>-5,05; 1,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,83</t>
+          <t>-2,26; 3,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,27</t>
+          <t>-3,66; 1,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,03</t>
+          <t>-2,88; 1,4</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,36</t>
+          <t>-1,4; 4,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,56</t>
+          <t>-3,97; 1,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,68</t>
+          <t>0,13; 5,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,31</t>
+          <t>-0,08; 5,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,88</t>
+          <t>-0,16; 3,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,76</t>
+          <t>-1,32; 2,49</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-0,9%</t>
+          <t>-1,21%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 4,56</t>
+          <t>-1,43; 4,92</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,71</t>
+          <t>-4,04; 1,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0,12; 6,21</t>
+          <t>0,14; 5,69</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,81</t>
+          <t>-0,1; 5,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,16</t>
+          <t>-0,16; 4,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,0</t>
+          <t>-1,36; 2,62</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,57</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,73</t>
+          <t>1,59; 9,15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,41; 10,12</t>
+          <t>2,2; 9,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,36</t>
+          <t>-1,51; 3,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,67</t>
+          <t>-3,24; 1,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,59</t>
+          <t>0,54; 4,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,87</t>
+          <t>-0,38; 3,47</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-0,79%</t>
+          <t>-0,91%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,46; 9,69</t>
+          <t>1,67; 10,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,36</t>
+          <t>2,27; 10,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,5</t>
+          <t>-1,48; 3,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,74</t>
+          <t>-3,29; 1,38</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,87</t>
+          <t>0,54; 4,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,11</t>
+          <t>-0,38; 3,71</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-6,91</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-1,6</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,58</t>
+          <t>-2,05; 1,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-25,67; -0,37</t>
+          <t>-4,49; -0,09</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,27</t>
+          <t>-2,08; 1,05</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,39</t>
+          <t>-2,64; 0,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,96</t>
+          <t>-1,55; 0,92</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -0,01</t>
+          <t>-3,08; -0,25</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-8,42%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1,36%</t>
+          <t>-1,24%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-4,64%</t>
+          <t>-1,88%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,95</t>
+          <t>-2,47; 1,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-31,08; -0,46</t>
+          <t>-5,42; -0,11</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,47</t>
+          <t>-2,35; 1,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,58</t>
+          <t>-2,99; 0,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,13</t>
+          <t>-1,81; 1,08</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-17,05; -0,02</t>
+          <t>-3,59; -0,29</t>
         </is>
       </c>
     </row>
